--- a/artfynd/A 20192-2022 artfynd.xlsx
+++ b/artfynd/A 20192-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20192-2022 artfynd.xlsx
+++ b/artfynd/A 20192-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,113 +789,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>112605117</v>
-      </c>
-      <c r="B3" t="n">
-        <v>78946</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Strömnäs, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>630450</v>
-      </c>
-      <c r="R3" t="n">
-        <v>7214553</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Stensele</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2022-11-30</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2022-11-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20192-2022 artfynd.xlsx
+++ b/artfynd/A 20192-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109910432</v>
+        <v>112605117</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>630449.5566507856</v>
+        <v>630450</v>
       </c>
       <c r="R2" t="n">
-        <v>7214553.354933015</v>
+        <v>7214553</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-11-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-11-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
